--- a/productos.xlsx
+++ b/productos.xlsx
@@ -11,12 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>nombre</t>
   </si>
   <si>
     <t>imagen</t>
+  </si>
+  <si>
+    <t>precio</t>
   </si>
   <si>
     <t>Bolsitas manijas de papel (12x17x6.5)</t>
@@ -83,6 +86,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <sz val="11.0"/>
@@ -121,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -130,6 +136,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -363,133 +372,139 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="C2" s="3">
+        <v>800.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>11</v>
+      <c r="A9" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>11</v>
+      <c r="A11" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>11</v>
+      <c r="A12" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>16</v>
+      <c r="A13" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>16</v>
+      <c r="A15" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>16</v>
+      <c r="A16" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>16</v>
+      <c r="A17" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ed69f128e13f1129/Desktop/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{8B4141B2-8DAE-485A-8F7C-4C4AC464ABC0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7402F3FF-EE97-4D4E-A76B-343C000E753F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>nombre</t>
   </si>
@@ -31,97 +31,73 @@
     <t>precio</t>
   </si>
   <si>
-    <t>Bolsitas manijas de papel (12x17x6.5)</t>
-  </si>
-  <si>
-    <t>imagen1.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bolsitas golosineras con cordon (12x17x6.5) </t>
-  </si>
-  <si>
-    <t>imagen2.jpg</t>
-  </si>
-  <si>
-    <t>imagen3.jpg</t>
-  </si>
-  <si>
-    <t>imagen4.jpg</t>
-  </si>
-  <si>
-    <t>imagen5.jpg</t>
-  </si>
-  <si>
-    <t>imagen6.jpg</t>
-  </si>
-  <si>
-    <t>imagen7.jpg</t>
-  </si>
-  <si>
-    <t>Topper mesa dulce x 5 piezas</t>
-  </si>
-  <si>
-    <t>imagen8.jpg</t>
-  </si>
-  <si>
-    <t>imagen9.jpg</t>
-  </si>
-  <si>
-    <t>imagen10.jpg</t>
-  </si>
-  <si>
-    <t>imagen11.jpg</t>
-  </si>
-  <si>
-    <t>Bolsita solapa mas broche</t>
-  </si>
-  <si>
-    <t>imagen12.jpg</t>
-  </si>
-  <si>
-    <t>imagen13.jpg</t>
-  </si>
-  <si>
-    <t>imagen14.jpg</t>
-  </si>
-  <si>
-    <t>imagen15.jpg</t>
-  </si>
-  <si>
-    <t>imagen16.jpg</t>
-  </si>
-  <si>
-    <t>imagen17.jpg</t>
-  </si>
-  <si>
-    <t>imagen18.jpg</t>
-  </si>
-  <si>
-    <t>imagen19.jpg</t>
-  </si>
-  <si>
-    <t>imagen20.jpg</t>
-  </si>
-  <si>
-    <t>centro de mesa hexagonal</t>
+    <t>imagen1.jpg,imagen1a.jpg,imagen1b.jpg,imagen1c.jpg</t>
+  </si>
+  <si>
+    <t>Bolsitas manijas de papel (12x17x6.5) x 10 unidades</t>
+  </si>
+  <si>
+    <t>$7500</t>
+  </si>
+  <si>
+    <t>imagen2.jpg,imagen2a.jpg,imagen2b.jpg,imagen2b.jpg</t>
+  </si>
+  <si>
+    <t>Bolsitas golosineras con cordon (12x17x6.5) x 10 unidades</t>
+  </si>
+  <si>
+    <t>$7.000</t>
+  </si>
+  <si>
+    <t>imagen3.jpg,imagen3a.jpg,imagen3b.jpg,imagen3c.jpg,imagen3d.jpg</t>
+  </si>
+  <si>
+    <t>Bolsitas con solapa (13x20x7.5) x10 unidades</t>
+  </si>
+  <si>
+    <t>$9500</t>
+  </si>
+  <si>
+    <t>topper mesa dulce x 5 piezas</t>
   </si>
   <si>
     <t>$2500</t>
   </si>
   <si>
-    <t>bolsita de papel fotografico simple</t>
-  </si>
-  <si>
-    <t>imagen21.jpg</t>
+    <t>imagen4.jpg,imagen4a.jpg,imagen4b.jpg,imagen4c.jpg</t>
+  </si>
+  <si>
+    <t>$6.000</t>
+  </si>
+  <si>
+    <t>imagen5.jpg,imagen5a.jpg,imagen5b.jpg</t>
+  </si>
+  <si>
+    <t>centros de mesa hexaganonal/tematica cualquiera, personalizada x 2 unidades</t>
+  </si>
+  <si>
+    <t>$13.000</t>
+  </si>
+  <si>
+    <t>Bolsitas estilo valija papel brilloso fotograf.(22x15x7cm) x10 unidades</t>
+  </si>
+  <si>
+    <t>imagen6.jpg,imagen6a.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolsitas pequeñas golosineras(10x16x4.5) sin manijas x10 unidades  </t>
+  </si>
+  <si>
+    <t>$5.000</t>
+  </si>
+  <si>
+    <t>imagen7.jpg,imagen7a.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -137,31 +113,27 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -184,18 +156,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,216 +388,204 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1000"/>
+  <dimension ref="A1:D1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.109375" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" customWidth="1"/>
-    <col min="3" max="26" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="43.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" customWidth="1"/>
+    <col min="3" max="3" width="66.44140625" customWidth="1"/>
+    <col min="4" max="4" width="29.77734375" customWidth="1"/>
+    <col min="5" max="26" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="5"/>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ed69f128e13f1129/Desktop/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7402F3FF-EE97-4D4E-A76B-343C000E753F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{67A72B9F-0C17-4C20-9AB6-D06889CD0B29}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>nombre</t>
   </si>
@@ -37,48 +37,30 @@
     <t>Bolsitas manijas de papel (12x17x6.5) x 10 unidades</t>
   </si>
   <si>
-    <t>$7500</t>
-  </si>
-  <si>
     <t>imagen2.jpg,imagen2a.jpg,imagen2b.jpg,imagen2b.jpg</t>
   </si>
   <si>
     <t>Bolsitas golosineras con cordon (12x17x6.5) x 10 unidades</t>
   </si>
   <si>
-    <t>$7.000</t>
-  </si>
-  <si>
     <t>imagen3.jpg,imagen3a.jpg,imagen3b.jpg,imagen3c.jpg,imagen3d.jpg</t>
   </si>
   <si>
     <t>Bolsitas con solapa (13x20x7.5) x10 unidades</t>
   </si>
   <si>
-    <t>$9500</t>
-  </si>
-  <si>
     <t>topper mesa dulce x 5 piezas</t>
   </si>
   <si>
-    <t>$2500</t>
-  </si>
-  <si>
     <t>imagen4.jpg,imagen4a.jpg,imagen4b.jpg,imagen4c.jpg</t>
   </si>
   <si>
-    <t>$6.000</t>
-  </si>
-  <si>
     <t>imagen5.jpg,imagen5a.jpg,imagen5b.jpg</t>
   </si>
   <si>
     <t>centros de mesa hexaganonal/tematica cualquiera, personalizada x 2 unidades</t>
   </si>
   <si>
-    <t>$13.000</t>
-  </si>
-  <si>
     <t>Bolsitas estilo valija papel brilloso fotograf.(22x15x7cm) x10 unidades</t>
   </si>
   <si>
@@ -86,9 +68,6 @@
   </si>
   <si>
     <t xml:space="preserve">Bolsitas pequeñas golosineras(10x16x4.5) sin manijas x10 unidades  </t>
-  </si>
-  <si>
-    <t>$5.000</t>
   </si>
   <si>
     <t>imagen7.jpg,imagen7a.jpg</t>
@@ -156,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -167,6 +146,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -414,8 +396,8 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
+      <c r="B2" s="2">
+        <v>7500</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -424,73 +406,73 @@
     </row>
     <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="B3" s="6">
+        <v>7000</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2">
+        <v>9500</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2500</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="B6" s="6">
+        <v>6000</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
+      </c>
+      <c r="B7" s="6">
+        <v>13000</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="B8" s="6">
+        <v>5000</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D8" s="2"/>
     </row>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ed69f128e13f1129/Desktop/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{67A72B9F-0C17-4C20-9AB6-D06889CD0B29}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{6721EED9-3C4B-466E-AAC1-504C37D6EA43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>nombre</t>
   </si>
@@ -34,21 +34,12 @@
     <t>imagen1.jpg,imagen1a.jpg,imagen1b.jpg,imagen1c.jpg</t>
   </si>
   <si>
-    <t>Bolsitas manijas de papel (12x17x6.5) x 10 unidades</t>
-  </si>
-  <si>
     <t>imagen2.jpg,imagen2a.jpg,imagen2b.jpg,imagen2b.jpg</t>
   </si>
   <si>
-    <t>Bolsitas golosineras con cordon (12x17x6.5) x 10 unidades</t>
-  </si>
-  <si>
     <t>imagen3.jpg,imagen3a.jpg,imagen3b.jpg,imagen3c.jpg,imagen3d.jpg</t>
   </si>
   <si>
-    <t>Bolsitas con solapa (13x20x7.5) x10 unidades</t>
-  </si>
-  <si>
     <t>topper mesa dulce x 5 piezas</t>
   </si>
   <si>
@@ -58,19 +49,40 @@
     <t>imagen5.jpg,imagen5a.jpg,imagen5b.jpg</t>
   </si>
   <si>
-    <t>centros de mesa hexaganonal/tematica cualquiera, personalizada x 2 unidades</t>
-  </si>
-  <si>
-    <t>Bolsitas estilo valija papel brilloso fotograf.(22x15x7cm) x10 unidades</t>
-  </si>
-  <si>
     <t>imagen6.jpg,imagen6a.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Bolsitas pequeñas golosineras(10x16x4.5) sin manijas x10 unidades  </t>
-  </si>
-  <si>
     <t>imagen7.jpg,imagen7a.jpg</t>
+  </si>
+  <si>
+    <t>bolsitas golosineras grandes(13x21x8) sin cordon (solo por mayor min 10 und)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolsitas pequeñas golosineras(10x16x4.5) sin manijas  (solo por mayor min 10 und)  </t>
+  </si>
+  <si>
+    <t>Bolsitas estilo valija papel brilloso fotograf.(22x15x7cm)  (solo por mayor min 10 und)</t>
+  </si>
+  <si>
+    <t>centros de mesa hexaganonal/tematica cualquiera, personalizada (solo x 2 und min)</t>
+  </si>
+  <si>
+    <t>imagen8.jpg,imagen8a.jpg,imagen8b.jpg</t>
+  </si>
+  <si>
+    <t>bolsitas golosineras grandes(13x21x8) con cordon (solo por mayor min 10 und)</t>
+  </si>
+  <si>
+    <t>imagen9.jpg,imagen9a.jpg</t>
+  </si>
+  <si>
+    <t>Bolsitas con solapa (13x20x7.5) (solo por mayor min 10 und)</t>
+  </si>
+  <si>
+    <t>Bolsitas golosineras con cordon (12x17x6.5) (solo por mayor min 10 und)</t>
+  </si>
+  <si>
+    <t>Bolsitas manijas de papel (12x17x6.5) (solo por mayor min 10 und)</t>
   </si>
 </sst>
 </file>
@@ -373,7 +385,7 @@
   <dimension ref="A1:D1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.88671875" customWidth="1"/>
+    <col min="1" max="1" width="65.88671875" customWidth="1"/>
     <col min="2" max="2" width="15.5546875" customWidth="1"/>
     <col min="3" max="3" width="66.44140625" customWidth="1"/>
     <col min="4" max="4" width="29.77734375" customWidth="1"/>
@@ -394,61 +406,61 @@
     </row>
     <row r="2" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2">
-        <v>7500</v>
+        <v>750</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B3" s="6">
-        <v>7000</v>
+        <v>700</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2">
-        <v>9500</v>
+        <v>1000</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2">
         <v>2500</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" s="6">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -457,35 +469,47 @@
         <v>13</v>
       </c>
       <c r="B7" s="6">
-        <v>13000</v>
+        <v>1300</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B8" s="6">
         <v>5000</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2">
+        <v>850</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="B10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ed69f128e13f1129/Desktop/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{6721EED9-3C4B-466E-AAC1-504C37D6EA43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{2D793B50-7C75-4200-B913-750ED46A39BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,9 +67,6 @@
     <t>centros de mesa hexaganonal/tematica cualquiera, personalizada (solo x 2 und min)</t>
   </si>
   <si>
-    <t>imagen8.jpg,imagen8a.jpg,imagen8b.jpg</t>
-  </si>
-  <si>
     <t>bolsitas golosineras grandes(13x21x8) con cordon (solo por mayor min 10 und)</t>
   </si>
   <si>
@@ -83,6 +80,9 @@
   </si>
   <si>
     <t>Bolsitas manijas de papel (12x17x6.5) (solo por mayor min 10 und)</t>
+  </si>
+  <si>
+    <t>imagen8.jpg,imagen8a.jpg,imagen8b.jpg,imagen8c.jpg</t>
   </si>
 </sst>
 </file>
@@ -406,7 +406,7 @@
     </row>
     <row r="2" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>750</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="3" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="6">
         <v>700</v>
@@ -430,7 +430,7 @@
     </row>
     <row r="4" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2">
         <v>1000</v>
@@ -488,27 +488,27 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2">
+        <v>850</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1000</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D10" s="2"/>
     </row>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ed69f128e13f1129/Desktop/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{2D793B50-7C75-4200-B913-750ED46A39BB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{912CDD6B-AE57-49C9-A377-B2B1BCCCC396}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>nombre</t>
   </si>
@@ -55,34 +55,40 @@
     <t>imagen7.jpg,imagen7a.jpg</t>
   </si>
   <si>
-    <t>bolsitas golosineras grandes(13x21x8) sin cordon (solo por mayor min 10 und)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bolsitas pequeñas golosineras(10x16x4.5) sin manijas  (solo por mayor min 10 und)  </t>
-  </si>
-  <si>
-    <t>Bolsitas estilo valija papel brilloso fotograf.(22x15x7cm)  (solo por mayor min 10 und)</t>
-  </si>
-  <si>
-    <t>centros de mesa hexaganonal/tematica cualquiera, personalizada (solo x 2 und min)</t>
-  </si>
-  <si>
     <t>bolsitas golosineras grandes(13x21x8) con cordon (solo por mayor min 10 und)</t>
   </si>
   <si>
     <t>imagen9.jpg,imagen9a.jpg</t>
   </si>
   <si>
-    <t>Bolsitas con solapa (13x20x7.5) (solo por mayor min 10 und)</t>
-  </si>
-  <si>
-    <t>Bolsitas golosineras con cordon (12x17x6.5) (solo por mayor min 10 und)</t>
-  </si>
-  <si>
-    <t>Bolsitas manijas de papel (12x17x6.5) (solo por mayor min 10 und)</t>
-  </si>
-  <si>
     <t>imagen8.jpg,imagen8a.jpg,imagen8b.jpg,imagen8c.jpg</t>
+  </si>
+  <si>
+    <t>bolsitas golosineras grandes(13x21x8) sin cordon (min 10 und)</t>
+  </si>
+  <si>
+    <t>bolsitas tienda/emprendimientos, personalizadas con tu logo (min 6 und)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolsitas pequeñas golosineras(10x16x4.5) sin manijas  ( min 10 und)  </t>
+  </si>
+  <si>
+    <t>Bolsitas estilo valija papel brilloso fotograf.(22x15x7cm)  (min 10 und)</t>
+  </si>
+  <si>
+    <t>centros de mesa hexaganonal/tematica cualquiera, personalizada ( min 2 und)</t>
+  </si>
+  <si>
+    <t>Bolsitas con solapa (13x20x7.5) (min 10 und)</t>
+  </si>
+  <si>
+    <t>Bolsitas golosineras con cordon (12x17x6.5) (min 10 und)</t>
+  </si>
+  <si>
+    <t>Bolsitas manijas de papel (12x17x6.5) (min 10 und)</t>
+  </si>
+  <si>
+    <t>imagen10.jpg,imagen10a.jpg,imagen10b.jpg,imagen10c.jpg,imagen10d.jpg</t>
   </si>
 </sst>
 </file>
@@ -406,7 +412,7 @@
     </row>
     <row r="2" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2">
         <v>750</v>
@@ -418,7 +424,7 @@
     </row>
     <row r="3" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="6">
         <v>700</v>
@@ -430,7 +436,7 @@
     </row>
     <row r="4" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2">
         <v>1000</v>
@@ -452,9 +458,9 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B6" s="6">
         <v>3000</v>
@@ -464,9 +470,9 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" s="6">
         <v>1300</v>
@@ -476,9 +482,9 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B8" s="6">
         <v>5000</v>
@@ -490,32 +496,38 @@
     </row>
     <row r="9" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2">
         <v>1000</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2">
         <v>850</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1500</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ed69f128e13f1129/Desktop/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{912CDD6B-AE57-49C9-A377-B2B1BCCCC396}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{F35A6F30-41F9-4A20-859D-B9B8635384DC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>nombre</t>
   </si>
@@ -49,9 +49,6 @@
     <t>imagen5.jpg,imagen5a.jpg,imagen5b.jpg</t>
   </si>
   <si>
-    <t>imagen6.jpg,imagen6a.jpg</t>
-  </si>
-  <si>
     <t>imagen7.jpg,imagen7a.jpg</t>
   </si>
   <si>
@@ -89,6 +86,33 @@
   </si>
   <si>
     <t>imagen10.jpg,imagen10a.jpg,imagen10b.jpg,imagen10c.jpg,imagen10d.jpg</t>
+  </si>
+  <si>
+    <t>imagen6.jpg,imagen6a.jpg,imagen6b.jpg</t>
+  </si>
+  <si>
+    <t>tazas golosineras hegagonales (10x11.5) opalina (min 10 und)</t>
+  </si>
+  <si>
+    <t>imagen11.jpg, imagen11a.jpg</t>
+  </si>
+  <si>
+    <t>numeros de mesa (min 5 und)</t>
+  </si>
+  <si>
+    <t>imagen12.jpg,imagen12a.jpg,imagen12b.jpg</t>
+  </si>
+  <si>
+    <t>platitos decorativos para mesa dulce(20.5x20.5) fotografico laminado (min 5 und)</t>
+  </si>
+  <si>
+    <t>imagen13.jpg</t>
+  </si>
+  <si>
+    <t>tarjetas personales para tu negocio, emprendimiento o para darle un toque especial a tus ventas (5x8) (min 10 und)</t>
+  </si>
+  <si>
+    <t>imagen14.jpg,imagen14a.jpg,imagen14b.jpg,imagen14c.jpg,imagen14d.jpg,</t>
   </si>
 </sst>
 </file>
@@ -391,7 +415,7 @@
   <dimension ref="A1:D1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="65.88671875" customWidth="1"/>
+    <col min="1" max="1" width="76.109375" customWidth="1"/>
     <col min="2" max="2" width="15.5546875" customWidth="1"/>
     <col min="3" max="3" width="66.44140625" customWidth="1"/>
     <col min="4" max="4" width="29.77734375" customWidth="1"/>
@@ -412,7 +436,7 @@
     </row>
     <row r="2" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2">
         <v>750</v>
@@ -424,7 +448,7 @@
     </row>
     <row r="3" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="6">
         <v>700</v>
@@ -436,7 +460,7 @@
     </row>
     <row r="4" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2">
         <v>1000</v>
@@ -460,7 +484,7 @@
     </row>
     <row r="6" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="6">
         <v>3000</v>
@@ -472,86 +496,110 @@
     </row>
     <row r="7" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="6">
         <v>1300</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="6">
         <v>5000</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="2">
         <v>1000</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2">
         <v>850</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2">
         <v>1500</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="2">
+        <v>480</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="2">
+        <v>680</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+    <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="2">
+        <v>700</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+    <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="2">
+        <v>350</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ed69f128e13f1129/Desktop/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{F35A6F30-41F9-4A20-859D-B9B8635384DC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{A014E4C9-629A-481A-9DFD-3084C1AA37F1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>nombre</t>
   </si>
@@ -43,9 +43,6 @@
     <t>topper mesa dulce x 5 piezas</t>
   </si>
   <si>
-    <t>imagen4.jpg,imagen4a.jpg,imagen4b.jpg,imagen4c.jpg</t>
-  </si>
-  <si>
     <t>imagen5.jpg,imagen5a.jpg,imagen5b.jpg</t>
   </si>
   <si>
@@ -112,14 +109,35 @@
     <t>tarjetas personales para tu negocio, emprendimiento o para darle un toque especial a tus ventas (5x8) (min 10 und)</t>
   </si>
   <si>
-    <t>imagen14.jpg,imagen14a.jpg,imagen14b.jpg,imagen14c.jpg,imagen14d.jpg,</t>
+    <t>imagen14.jpg,imagen14a.jpg,imagen14b.jpg,imagen14c.jpg</t>
+  </si>
+  <si>
+    <t>imagen15.jpg, imagen15a.jpg, imagen15b.jpg, imagen15c.jpg, imagen15d.jpg, imagen15e.jpg, imagen15f.jpg</t>
+  </si>
+  <si>
+    <t>banderin tamaño chico para tu evento, personalizado</t>
+  </si>
+  <si>
+    <t>banderin grande para tu evente, personalizado</t>
+  </si>
+  <si>
+    <t>imagen16.jpg,imagen16a.jpg,imagen16b.jpg</t>
+  </si>
+  <si>
+    <t>cajitas milk (10x21) min 10 und (broche o cinta de razo a elección)</t>
+  </si>
+  <si>
+    <t>imagen17.jpg,imagen17a.jpg,imagen17b.jpg,imagen17c.jpg,imagen17d.jpg,imagen17e.jpg,imagen17f.jpg,imagen17g.jpg</t>
+  </si>
+  <si>
+    <t>imagen4.jpg,imagen4a.jpg,imagen4b.jpg,imagen4c.jpg,imagen4d.jpg,imagen4e.jpg,imagen4f.jpg,imagen4g.jpg,imagen4h.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,12 +166,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -177,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -185,9 +197,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -417,7 +428,7 @@
   <cols>
     <col min="1" max="1" width="76.109375" customWidth="1"/>
     <col min="2" max="2" width="15.5546875" customWidth="1"/>
-    <col min="3" max="3" width="66.44140625" customWidth="1"/>
+    <col min="3" max="3" width="104.5546875" customWidth="1"/>
     <col min="4" max="4" width="29.77734375" customWidth="1"/>
     <col min="5" max="26" width="10.6640625" customWidth="1"/>
   </cols>
@@ -436,7 +447,7 @@
     </row>
     <row r="2" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>750</v>
@@ -448,9 +459,9 @@
     </row>
     <row r="3" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="6">
+        <v>18</v>
+      </c>
+      <c r="B3" s="5">
         <v>700</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -460,7 +471,7 @@
     </row>
     <row r="4" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2">
         <v>1000</v>
@@ -477,146 +488,165 @@
       <c r="B5" s="2">
         <v>2500</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
+      <c r="C5" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="6">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5">
         <v>3000</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="6">
+        <v>15</v>
+      </c>
+      <c r="B7" s="5">
         <v>1300</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="6">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5">
         <v>5000</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2">
         <v>1000</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2">
         <v>850</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2">
         <v>1500</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2">
         <v>480</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2">
         <v>680</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="B14" s="2">
         <v>700</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2">
         <v>350</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="2">
+        <v>6500</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="A17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="5">
+        <v>10000</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="5">
+        <v>1000</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
@@ -625,22 +655,22 @@
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4">
         <v>8</v>
       </c>
-      <c r="D22" s="5"/>
+      <c r="D22" s="4"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ed69f128e13f1129/Desktop/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{A014E4C9-629A-481A-9DFD-3084C1AA37F1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{2D0AD353-DD3C-4E08-98F7-F9B9FAF2CBE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,9 +82,6 @@
     <t>Bolsitas manijas de papel (12x17x6.5) (min 10 und)</t>
   </si>
   <si>
-    <t>imagen10.jpg,imagen10a.jpg,imagen10b.jpg,imagen10c.jpg,imagen10d.jpg</t>
-  </si>
-  <si>
     <t>imagen6.jpg,imagen6a.jpg,imagen6b.jpg</t>
   </si>
   <si>
@@ -131,6 +128,9 @@
   </si>
   <si>
     <t>imagen4.jpg,imagen4a.jpg,imagen4b.jpg,imagen4c.jpg,imagen4d.jpg,imagen4e.jpg,imagen4f.jpg,imagen4g.jpg,imagen4h.jpg</t>
+  </si>
+  <si>
+    <t>imagen10.jpg,imagen10a.jpg,imagen10b.jpg,imagen10c.jpg,imagen10d.jpg,imagen10e.jpg</t>
   </si>
 </sst>
 </file>
@@ -489,7 +489,7 @@
         <v>2500</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -513,7 +513,7 @@
         <v>1300</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -561,91 +561,91 @@
         <v>1500</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2">
         <v>480</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2">
         <v>680</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2">
         <v>700</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2">
         <v>350</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2">
         <v>6500</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="5">
         <v>10000</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="B18" s="5">
         <v>1000</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" s="2"/>
     </row>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ed69f128e13f1129/Desktop/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{2D0AD353-DD3C-4E08-98F7-F9B9FAF2CBE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="14_{E54C04C9-325C-487C-9794-7EAFE59853E1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{5A7BB015-CDAF-4874-A3F1-5F7EA213BD87}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>nombre</t>
   </si>
@@ -31,9 +31,6 @@
     <t>precio</t>
   </si>
   <si>
-    <t>imagen1.jpg,imagen1a.jpg,imagen1b.jpg,imagen1c.jpg</t>
-  </si>
-  <si>
     <t>imagen2.jpg,imagen2a.jpg,imagen2b.jpg,imagen2b.jpg</t>
   </si>
   <si>
@@ -115,9 +112,6 @@
     <t>banderin tamaño chico para tu evento, personalizado</t>
   </si>
   <si>
-    <t>banderin grande para tu evente, personalizado</t>
-  </si>
-  <si>
     <t>imagen16.jpg,imagen16a.jpg,imagen16b.jpg</t>
   </si>
   <si>
@@ -131,6 +125,18 @@
   </si>
   <si>
     <t>imagen10.jpg,imagen10a.jpg,imagen10b.jpg,imagen10c.jpg,imagen10d.jpg,imagen10e.jpg</t>
+  </si>
+  <si>
+    <t>imagen1.jpg,imagen1a.jpg,imagen1b.jpg,imagen1c.jpg,imagen1d.jpg</t>
+  </si>
+  <si>
+    <t>libritos para colorear (min 8 und) medidas 15.5x21</t>
+  </si>
+  <si>
+    <t>imagen18.jpg,imagen18a.jpg,imagen18b.jpg,imagen18c.jpg,</t>
+  </si>
+  <si>
+    <t>banderin tamaño grande para tu evento, personalizado</t>
   </si>
 </sst>
 </file>
@@ -447,211 +453,218 @@
     </row>
     <row r="2" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2">
         <v>750</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="5">
         <v>700</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2">
         <v>1000</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
         <v>2500</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="5">
         <v>3000</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="5">
         <v>1300</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5">
         <v>5000</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2">
         <v>1000</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2">
         <v>850</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="2">
         <v>1500</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2">
         <v>480</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2">
         <v>680</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2">
         <v>700</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2">
         <v>350</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" s="2">
         <v>6500</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5">
         <v>10000</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B18" s="5">
         <v>1000</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="2">
+        <v>580</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -667,9 +680,7 @@
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4"/>
-      <c r="C22" s="4">
-        <v>8</v>
-      </c>
+      <c r="C22" s="4"/>
       <c r="D22" s="4"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ed69f128e13f1129/Desktop/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="14_{E54C04C9-325C-487C-9794-7EAFE59853E1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{5A7BB015-CDAF-4874-A3F1-5F7EA213BD87}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{A4DB30D2-F198-4796-B39B-28E5AEB1C68D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>nombre</t>
   </si>
@@ -137,6 +137,18 @@
   </si>
   <si>
     <t>banderin tamaño grande para tu evento, personalizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caja/box 13x14 (min 10 und) personalizado </t>
+  </si>
+  <si>
+    <t>imagen19.jpg,imagen19a.jpg,imagen19b.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caja/box con visor (alto 5cm, ancho 22cm, laterales (min 10 und) personalizado </t>
+  </si>
+  <si>
+    <t>imagen20.jpg,imagen20a.jpg</t>
   </si>
 </sst>
 </file>
@@ -203,13 +215,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,7 +479,7 @@
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>700</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -494,7 +506,7 @@
       <c r="B5" s="2">
         <v>2500</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="2"/>
@@ -503,7 +515,7 @@
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>3000</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -515,7 +527,7 @@
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>1300</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -527,7 +539,7 @@
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>5000</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -620,43 +632,43 @@
       <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="2">
         <v>6500</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>10000</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>1000</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="2">
@@ -668,20 +680,33 @@
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
+      <c r="A20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="3">
+        <v>750</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3">
+        <v>820</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ed69f128e13f1129/Desktop/tienda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{A4DB30D2-F198-4796-B39B-28E5AEB1C68D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{222E1589-7D35-4F7E-9888-315B9A736183}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>nombre</t>
   </si>
@@ -40,9 +40,6 @@
     <t>topper mesa dulce x 5 piezas</t>
   </si>
   <si>
-    <t>imagen5.jpg,imagen5a.jpg,imagen5b.jpg</t>
-  </si>
-  <si>
     <t>imagen7.jpg,imagen7a.jpg</t>
   </si>
   <si>
@@ -149,6 +146,39 @@
   </si>
   <si>
     <t>imagen20.jpg,imagen20a.jpg</t>
+  </si>
+  <si>
+    <t>pulseras de papel horografico (min 10 unidades) 20cm largo 3cm ancho</t>
+  </si>
+  <si>
+    <t>imagen21.jpg,imagen21a.jpg,imagen21b.jpg,imagen21c.jpg,imagen21d.jpg,imagen21e.jpg</t>
+  </si>
+  <si>
+    <t>imagen5.jpg,imagen5a.jpg,imagen5b.jpg,imagen5b.jpg,imagen5c.jpg,imagen5d.jpg,imagen5e.jpg</t>
+  </si>
+  <si>
+    <t>libritos para colorear (min 8 und) + lapices de colorear</t>
+  </si>
+  <si>
+    <t>imagen22.jpg,imagen22a.jpg,imagen22b.jpg</t>
+  </si>
+  <si>
+    <t>separadores escolares para carpeta (min 3 und)</t>
+  </si>
+  <si>
+    <t>imagen23.jpg,imagen23a.jpg,imagen23b.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">planchas de stickers a4 comun </t>
+  </si>
+  <si>
+    <t>imagen24.jpg,imagen23a.jpg.imagen23b.jpg</t>
+  </si>
+  <si>
+    <t>planchas de stickers resistentes al agua</t>
+  </si>
+  <si>
+    <t>imagen25.jpg,imagen25a.jpg,imagen25b.jpg</t>
   </si>
 </sst>
 </file>
@@ -465,19 +495,19 @@
     </row>
     <row r="2" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2">
         <v>750</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4">
         <v>700</v>
@@ -489,7 +519,7 @@
     </row>
     <row r="4" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2">
         <v>1000</v>
@@ -507,211 +537,258 @@
         <v>2500</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="4">
         <v>3000</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4">
         <v>1300</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="4">
         <v>5000</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2">
         <v>1000</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2">
         <v>850</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2">
         <v>1500</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2">
         <v>480</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2">
         <v>680</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2">
         <v>700</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2">
         <v>350</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2">
         <v>6500</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="4">
         <v>10000</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="4">
         <v>1000</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2">
+        <v>600</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" s="2">
-        <v>580</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="2">
+        <v>580</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="B20" s="3">
-        <v>750</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="2">
+        <v>580</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3">
-        <v>820</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
+      <c r="B22" s="2">
+        <v>580</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1300</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1500</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2000</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="2">
+        <v>2500</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -3,10 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Hoja1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Hoja1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="oWuD1zvwZmL64rkWPH2h/jGrJSWMFwT8uzve+Q1F0nM="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -175,7 +180,7 @@
     <t xml:space="preserve">servilleteros </t>
   </si>
   <si>
-    <t>imagen26.jpg,imagen26b.jpg</t>
+    <t>imagen26.jpg,imagen26a.jpg</t>
   </si>
   <si>
     <t>fotos polaroid/recuerdos imantadas</t>
@@ -269,10 +274,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ED69F128E13F1129/Desktop/tienda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisf\OneDrive\Desktop\tienda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_CC154315B56AC98CE9917670F3AE16F0ED66A72A" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{33786940-3F9B-43C7-8A9A-49BFFB86B8BC}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_CC154315B56AC98CE9917670F3AE16F0ED66A72A" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{34650B97-184B-4B86-A548-825AD9A3FF90}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>nombre</t>
   </si>
@@ -201,9 +201,6 @@
     <t>imagen28.jpg,imagen28a.jpg,imagen28b.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">llaveros plastico/resina </t>
-  </si>
-  <si>
     <t xml:space="preserve">vasos sorbete + stickers resistente al agua </t>
   </si>
   <si>
@@ -216,9 +213,6 @@
     <t>imagen30.jpg,imagen30a.jpg</t>
   </si>
   <si>
-    <t>imagen32.jpg</t>
-  </si>
-  <si>
     <t>centro de  mesa florar 1 sin base + stickers</t>
   </si>
   <si>
@@ -259,6 +253,9 @@
   </si>
   <si>
     <t>imagen8.jpg,imagen8a.jpg,imagen8b.jpg,imagen8c.jpg,imagen8d.jpg,imagen8e.jpg</t>
+  </si>
+  <si>
+    <t>imagen32.jpg,imagen32a.jpg</t>
   </si>
 </sst>
 </file>
@@ -659,7 +656,7 @@
         <v>1200</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -897,11 +894,14 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" t="s">
         <v>58</v>
       </c>
       <c r="B30" s="8">
-        <v>2500</v>
+        <v>1800</v>
+      </c>
+      <c r="C30" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -909,7 +909,7 @@
         <v>59</v>
       </c>
       <c r="B31">
-        <v>1800</v>
+        <v>2500</v>
       </c>
       <c r="C31" t="s">
         <v>61</v>
@@ -917,13 +917,13 @@
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B32">
-        <v>2500</v>
+        <v>14000</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -931,43 +931,43 @@
         <v>64</v>
       </c>
       <c r="B33">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B34">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="C34" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B35">
-        <v>20000</v>
+        <v>35000</v>
       </c>
       <c r="C35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B36">
-        <v>350000</v>
+        <v>16000</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -975,7 +975,7 @@
         <v>72</v>
       </c>
       <c r="B37">
-        <v>16000</v>
+        <v>30000</v>
       </c>
       <c r="C37" t="s">
         <v>71</v>
@@ -986,23 +986,13 @@
         <v>74</v>
       </c>
       <c r="B38">
-        <v>30000</v>
+        <v>12000</v>
       </c>
       <c r="C38" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39">
-        <v>12000</v>
-      </c>
-      <c r="C39" t="s">
-        <v>75</v>
-      </c>
-    </row>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
